--- a/web/public/forms/orig/o-hoeui-gongjeongpyo.xlsx
+++ b/web/public/forms/orig/o-hoeui-gongjeongpyo.xlsx
@@ -717,7 +717,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="S1" s="31" t="inlineStr">

--- a/web/public/forms/orig/o-hoeui-gongjeongpyo.xlsx
+++ b/web/public/forms/orig/o-hoeui-gongjeongpyo.xlsx
@@ -670,7 +670,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
